--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260713.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>156,305</t>
+          <t>155,535</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.06%</t>
+          <t>27.73%</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,835</t>
+          <t>17,715</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>113,200</t>
+          <t>112,700</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>6.88%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>57,795</t>
+          <t>57,295</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>5.79%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>137,755</t>
+          <t>137,065</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.63%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>67,760</t>
+          <t>67,420</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>74,295</t>
+          <t>73,945</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,525</t>
+          <t>6,425</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
@@ -787,56 +787,56 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>51,205</t>
+          <t>51,055</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>20,783</t>
+          <t>22,355</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>22,455</t>
+          <t>20,683</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,780</t>
+          <t>35,660</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -875,144 +875,144 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>87,355</t>
+          <t>86,915</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,995</t>
+          <t>57,675</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>57,965</t>
+          <t>22,895</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,090</t>
+          <t>22,070</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>22,170</t>
+          <t>30,028</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>30,178</t>
+          <t>40,900</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>8,990</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>67,258</t>
+          <t>67,108</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>10,866</t>
+          <t>13,151</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,44 +1085,44 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13,251</t>
+          <t>24,158</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,158</t>
+          <t>10,866</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>143,615</t>
+          <t>143,115</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>20,935</t>
+          <t>20,835</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1183,78 +1183,78 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,101</t>
+          <t>18,001</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>22,387</t>
+          <t>42,330</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,305</t>
+          <t>22,237</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,540</t>
+          <t>13,305</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>48,940</t>
+          <t>48,700</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,51 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>32,136,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>1,146,506</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
